--- a/testData/testData.xlsx
+++ b/testData/testData.xlsx
@@ -1,35 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cognizantonline-my.sharepoint.com/personal/2475087_cognizant_com/Documents/Documents/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3C38E0AE-C6AF-4B25-AA09-6930A2341E9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{37EE927B-9829-4A5F-B72E-C0665E1A6876}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{C26D8135-FAB3-4A71-B665-C86143E34343}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="0"/>
+  <oleSize ref="A1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="2"/>
     </ext>
   </extLst>
 </workbook>
@@ -62,28 +50,28 @@
     <t>interest</t>
   </si>
   <si>
+    <t>unknown</t>
+  </si>
+  <si>
+    <t>unknown organization</t>
+  </si>
+  <si>
+    <t>unknown@abc.com</t>
+  </si>
+  <si>
+    <t>&lt;500</t>
+  </si>
+  <si>
+    <t>Taking a demo</t>
+  </si>
+  <si>
+    <t>Identify Hospitals Data</t>
+  </si>
+  <si>
+    <t>Corporate Wellness Data</t>
+  </si>
+  <si>
     <t>Bangalore</t>
-  </si>
-  <si>
-    <t>unknown</t>
-  </si>
-  <si>
-    <t>unknown organization</t>
-  </si>
-  <si>
-    <t>unknown@abc.com</t>
-  </si>
-  <si>
-    <t>&lt;500</t>
-  </si>
-  <si>
-    <t>Taking a demo</t>
-  </si>
-  <si>
-    <t>Identify Hospitals Data</t>
-  </si>
-  <si>
-    <t>Corporate Wellness Data</t>
   </si>
 </sst>
 </file>
@@ -484,7 +472,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -498,7 +486,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
@@ -511,7 +499,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -525,7 +513,7 @@
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
@@ -533,7 +521,7 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
@@ -549,7 +537,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
@@ -557,7 +545,7 @@
         <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
@@ -565,7 +553,7 @@
         <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
